--- a/selenium_auto/fuels/params.xlsx
+++ b/selenium_auto/fuels/params.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Agdy\PycharmProjects\job\selenium_auto\fuels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C37D480-D9B7-448E-98D7-7FB64929F68A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C989204F-43CB-4BBD-86D1-E5B69E3FC67E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="18">
   <si>
     <t>Iot Id</t>
   </si>
@@ -80,21 +80,28 @@
   <si>
     <t>null</t>
   </si>
-  <si>
-    <t>Да</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -105,7 +112,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -113,16 +120,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF666666"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF666666"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF666666"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF666666"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{3CA6FBB9-58A5-4A29-B937-FEBB8043F611}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -400,7 +427,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P2"/>
+  <dimension ref="A1:P85"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.1796875" customWidth="1"/>
@@ -472,14 +499,14 @@
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>10157</v>
+      <c r="A2" s="2">
+        <v>3629</v>
       </c>
       <c r="B2" s="1">
-        <v>46054</v>
+        <v>46082</v>
       </c>
       <c r="C2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D2">
         <v>30</v>
@@ -518,6 +545,4156 @@
         <v>17</v>
       </c>
       <c r="P2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
+        <v>4636</v>
+      </c>
+      <c r="B3" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3">
+        <v>30</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>120</v>
+      </c>
+      <c r="H3">
+        <v>300</v>
+      </c>
+      <c r="I3">
+        <v>300</v>
+      </c>
+      <c r="J3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L3">
+        <v>120</v>
+      </c>
+      <c r="M3">
+        <v>16</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
+        <v>3592</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4">
+        <v>30</v>
+      </c>
+      <c r="E4">
+        <v>10</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4">
+        <v>120</v>
+      </c>
+      <c r="H4">
+        <v>300</v>
+      </c>
+      <c r="I4">
+        <v>300</v>
+      </c>
+      <c r="J4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L4">
+        <v>120</v>
+      </c>
+      <c r="M4">
+        <v>16</v>
+      </c>
+      <c r="N4" t="s">
+        <v>17</v>
+      </c>
+      <c r="O4" t="s">
+        <v>17</v>
+      </c>
+      <c r="P4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
+        <v>3307</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5">
+        <v>30</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>120</v>
+      </c>
+      <c r="H5">
+        <v>300</v>
+      </c>
+      <c r="I5">
+        <v>300</v>
+      </c>
+      <c r="J5" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5">
+        <v>120</v>
+      </c>
+      <c r="M5">
+        <v>16</v>
+      </c>
+      <c r="N5" t="s">
+        <v>17</v>
+      </c>
+      <c r="O5" t="s">
+        <v>17</v>
+      </c>
+      <c r="P5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
+        <v>4637</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6">
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>120</v>
+      </c>
+      <c r="H6">
+        <v>300</v>
+      </c>
+      <c r="I6">
+        <v>300</v>
+      </c>
+      <c r="J6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
+      <c r="L6">
+        <v>120</v>
+      </c>
+      <c r="M6">
+        <v>16</v>
+      </c>
+      <c r="N6" t="s">
+        <v>17</v>
+      </c>
+      <c r="O6" t="s">
+        <v>17</v>
+      </c>
+      <c r="P6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
+        <v>3266</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7">
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>10</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>120</v>
+      </c>
+      <c r="H7">
+        <v>300</v>
+      </c>
+      <c r="I7">
+        <v>300</v>
+      </c>
+      <c r="J7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" t="s">
+        <v>17</v>
+      </c>
+      <c r="L7">
+        <v>120</v>
+      </c>
+      <c r="M7">
+        <v>16</v>
+      </c>
+      <c r="N7" t="s">
+        <v>17</v>
+      </c>
+      <c r="O7" t="s">
+        <v>17</v>
+      </c>
+      <c r="P7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
+        <v>3297</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C8" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8">
+        <v>30</v>
+      </c>
+      <c r="E8">
+        <v>10</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8">
+        <v>120</v>
+      </c>
+      <c r="H8">
+        <v>300</v>
+      </c>
+      <c r="I8">
+        <v>300</v>
+      </c>
+      <c r="J8" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" t="s">
+        <v>17</v>
+      </c>
+      <c r="L8">
+        <v>120</v>
+      </c>
+      <c r="M8">
+        <v>16</v>
+      </c>
+      <c r="N8" t="s">
+        <v>17</v>
+      </c>
+      <c r="O8" t="s">
+        <v>17</v>
+      </c>
+      <c r="P8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
+        <v>4643</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C9" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9">
+        <v>30</v>
+      </c>
+      <c r="E9">
+        <v>10</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>120</v>
+      </c>
+      <c r="H9">
+        <v>300</v>
+      </c>
+      <c r="I9">
+        <v>300</v>
+      </c>
+      <c r="J9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9">
+        <v>120</v>
+      </c>
+      <c r="M9">
+        <v>16</v>
+      </c>
+      <c r="N9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O9" t="s">
+        <v>17</v>
+      </c>
+      <c r="P9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
+        <v>11788</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10">
+        <v>30</v>
+      </c>
+      <c r="E10">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>120</v>
+      </c>
+      <c r="H10">
+        <v>300</v>
+      </c>
+      <c r="I10">
+        <v>300</v>
+      </c>
+      <c r="J10" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" t="s">
+        <v>17</v>
+      </c>
+      <c r="L10">
+        <v>120</v>
+      </c>
+      <c r="M10">
+        <v>16</v>
+      </c>
+      <c r="N10" t="s">
+        <v>17</v>
+      </c>
+      <c r="O10" t="s">
+        <v>17</v>
+      </c>
+      <c r="P10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
+        <v>3628</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>120</v>
+      </c>
+      <c r="H11">
+        <v>300</v>
+      </c>
+      <c r="I11">
+        <v>300</v>
+      </c>
+      <c r="J11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L11">
+        <v>120</v>
+      </c>
+      <c r="M11">
+        <v>16</v>
+      </c>
+      <c r="N11" t="s">
+        <v>17</v>
+      </c>
+      <c r="O11" t="s">
+        <v>17</v>
+      </c>
+      <c r="P11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
+        <v>3596</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C12" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12">
+        <v>30</v>
+      </c>
+      <c r="E12">
+        <v>10</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12">
+        <v>120</v>
+      </c>
+      <c r="H12">
+        <v>300</v>
+      </c>
+      <c r="I12">
+        <v>300</v>
+      </c>
+      <c r="J12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12">
+        <v>120</v>
+      </c>
+      <c r="M12">
+        <v>16</v>
+      </c>
+      <c r="N12" t="s">
+        <v>17</v>
+      </c>
+      <c r="O12" t="s">
+        <v>17</v>
+      </c>
+      <c r="P12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
+        <v>3314</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C13" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13">
+        <v>30</v>
+      </c>
+      <c r="E13">
+        <v>10</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13">
+        <v>120</v>
+      </c>
+      <c r="H13">
+        <v>300</v>
+      </c>
+      <c r="I13">
+        <v>300</v>
+      </c>
+      <c r="J13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13">
+        <v>120</v>
+      </c>
+      <c r="M13">
+        <v>16</v>
+      </c>
+      <c r="N13" t="s">
+        <v>17</v>
+      </c>
+      <c r="O13" t="s">
+        <v>17</v>
+      </c>
+      <c r="P13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
+        <v>3278</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C14" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>10</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>120</v>
+      </c>
+      <c r="H14">
+        <v>300</v>
+      </c>
+      <c r="I14">
+        <v>300</v>
+      </c>
+      <c r="J14" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14">
+        <v>120</v>
+      </c>
+      <c r="M14">
+        <v>16</v>
+      </c>
+      <c r="N14" t="s">
+        <v>17</v>
+      </c>
+      <c r="O14" t="s">
+        <v>17</v>
+      </c>
+      <c r="P14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
+        <v>4363</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C15" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15">
+        <v>30</v>
+      </c>
+      <c r="E15">
+        <v>10</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15">
+        <v>120</v>
+      </c>
+      <c r="H15">
+        <v>300</v>
+      </c>
+      <c r="I15">
+        <v>300</v>
+      </c>
+      <c r="J15" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" t="s">
+        <v>17</v>
+      </c>
+      <c r="L15">
+        <v>120</v>
+      </c>
+      <c r="M15">
+        <v>16</v>
+      </c>
+      <c r="N15" t="s">
+        <v>17</v>
+      </c>
+      <c r="O15" t="s">
+        <v>17</v>
+      </c>
+      <c r="P15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
+        <v>4780</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C16" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16">
+        <v>30</v>
+      </c>
+      <c r="E16">
+        <v>10</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16">
+        <v>120</v>
+      </c>
+      <c r="H16">
+        <v>300</v>
+      </c>
+      <c r="I16">
+        <v>300</v>
+      </c>
+      <c r="J16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" t="s">
+        <v>17</v>
+      </c>
+      <c r="L16">
+        <v>120</v>
+      </c>
+      <c r="M16">
+        <v>16</v>
+      </c>
+      <c r="N16" t="s">
+        <v>17</v>
+      </c>
+      <c r="O16" t="s">
+        <v>17</v>
+      </c>
+      <c r="P16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
+        <v>4640</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C17" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17">
+        <v>30</v>
+      </c>
+      <c r="E17">
+        <v>10</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17">
+        <v>120</v>
+      </c>
+      <c r="H17">
+        <v>300</v>
+      </c>
+      <c r="I17">
+        <v>300</v>
+      </c>
+      <c r="J17" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" t="s">
+        <v>17</v>
+      </c>
+      <c r="L17">
+        <v>120</v>
+      </c>
+      <c r="M17">
+        <v>16</v>
+      </c>
+      <c r="N17" t="s">
+        <v>17</v>
+      </c>
+      <c r="O17" t="s">
+        <v>17</v>
+      </c>
+      <c r="P17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
+        <v>4639</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C18" t="s">
+        <v>16</v>
+      </c>
+      <c r="D18">
+        <v>30</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>120</v>
+      </c>
+      <c r="H18">
+        <v>300</v>
+      </c>
+      <c r="I18">
+        <v>300</v>
+      </c>
+      <c r="J18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" t="s">
+        <v>17</v>
+      </c>
+      <c r="L18">
+        <v>120</v>
+      </c>
+      <c r="M18">
+        <v>16</v>
+      </c>
+      <c r="N18" t="s">
+        <v>17</v>
+      </c>
+      <c r="O18" t="s">
+        <v>17</v>
+      </c>
+      <c r="P18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
+        <v>3272</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C19" t="s">
+        <v>16</v>
+      </c>
+      <c r="D19">
+        <v>30</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+      <c r="G19">
+        <v>120</v>
+      </c>
+      <c r="H19">
+        <v>300</v>
+      </c>
+      <c r="I19">
+        <v>300</v>
+      </c>
+      <c r="J19" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" t="s">
+        <v>17</v>
+      </c>
+      <c r="L19">
+        <v>120</v>
+      </c>
+      <c r="M19">
+        <v>16</v>
+      </c>
+      <c r="N19" t="s">
+        <v>17</v>
+      </c>
+      <c r="O19" t="s">
+        <v>17</v>
+      </c>
+      <c r="P19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
+        <v>3594</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C20" t="s">
+        <v>16</v>
+      </c>
+      <c r="D20">
+        <v>30</v>
+      </c>
+      <c r="E20">
+        <v>10</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20">
+        <v>120</v>
+      </c>
+      <c r="H20">
+        <v>300</v>
+      </c>
+      <c r="I20">
+        <v>300</v>
+      </c>
+      <c r="J20" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" t="s">
+        <v>17</v>
+      </c>
+      <c r="L20">
+        <v>120</v>
+      </c>
+      <c r="M20">
+        <v>16</v>
+      </c>
+      <c r="N20" t="s">
+        <v>17</v>
+      </c>
+      <c r="O20" t="s">
+        <v>17</v>
+      </c>
+      <c r="P20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
+        <v>3288</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D21">
+        <v>30</v>
+      </c>
+      <c r="E21">
+        <v>10</v>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21">
+        <v>120</v>
+      </c>
+      <c r="H21">
+        <v>300</v>
+      </c>
+      <c r="I21">
+        <v>300</v>
+      </c>
+      <c r="J21" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" t="s">
+        <v>17</v>
+      </c>
+      <c r="L21">
+        <v>120</v>
+      </c>
+      <c r="M21">
+        <v>16</v>
+      </c>
+      <c r="N21" t="s">
+        <v>17</v>
+      </c>
+      <c r="O21" t="s">
+        <v>17</v>
+      </c>
+      <c r="P21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
+        <v>3290</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C22" t="s">
+        <v>16</v>
+      </c>
+      <c r="D22">
+        <v>30</v>
+      </c>
+      <c r="E22">
+        <v>10</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22">
+        <v>120</v>
+      </c>
+      <c r="H22">
+        <v>300</v>
+      </c>
+      <c r="I22">
+        <v>300</v>
+      </c>
+      <c r="J22" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" t="s">
+        <v>17</v>
+      </c>
+      <c r="L22">
+        <v>120</v>
+      </c>
+      <c r="M22">
+        <v>16</v>
+      </c>
+      <c r="N22" t="s">
+        <v>17</v>
+      </c>
+      <c r="O22" t="s">
+        <v>17</v>
+      </c>
+      <c r="P22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
+        <v>3343</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23">
+        <v>30</v>
+      </c>
+      <c r="E23">
+        <v>10</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23">
+        <v>120</v>
+      </c>
+      <c r="H23">
+        <v>300</v>
+      </c>
+      <c r="I23">
+        <v>300</v>
+      </c>
+      <c r="J23" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23">
+        <v>120</v>
+      </c>
+      <c r="M23">
+        <v>16</v>
+      </c>
+      <c r="N23" t="s">
+        <v>17</v>
+      </c>
+      <c r="O23" t="s">
+        <v>17</v>
+      </c>
+      <c r="P23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
+        <v>3270</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C24" t="s">
+        <v>16</v>
+      </c>
+      <c r="D24">
+        <v>30</v>
+      </c>
+      <c r="E24">
+        <v>10</v>
+      </c>
+      <c r="F24">
+        <v>10</v>
+      </c>
+      <c r="G24">
+        <v>120</v>
+      </c>
+      <c r="H24">
+        <v>300</v>
+      </c>
+      <c r="I24">
+        <v>300</v>
+      </c>
+      <c r="J24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" t="s">
+        <v>17</v>
+      </c>
+      <c r="L24">
+        <v>120</v>
+      </c>
+      <c r="M24">
+        <v>16</v>
+      </c>
+      <c r="N24" t="s">
+        <v>17</v>
+      </c>
+      <c r="O24" t="s">
+        <v>17</v>
+      </c>
+      <c r="P24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
+        <v>3342</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D25">
+        <v>30</v>
+      </c>
+      <c r="E25">
+        <v>10</v>
+      </c>
+      <c r="F25">
+        <v>10</v>
+      </c>
+      <c r="G25">
+        <v>120</v>
+      </c>
+      <c r="H25">
+        <v>300</v>
+      </c>
+      <c r="I25">
+        <v>300</v>
+      </c>
+      <c r="J25" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" t="s">
+        <v>17</v>
+      </c>
+      <c r="L25">
+        <v>120</v>
+      </c>
+      <c r="M25">
+        <v>16</v>
+      </c>
+      <c r="N25" t="s">
+        <v>17</v>
+      </c>
+      <c r="O25" t="s">
+        <v>17</v>
+      </c>
+      <c r="P25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
+        <v>3593</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C26" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26">
+        <v>30</v>
+      </c>
+      <c r="E26">
+        <v>10</v>
+      </c>
+      <c r="F26">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>120</v>
+      </c>
+      <c r="H26">
+        <v>300</v>
+      </c>
+      <c r="I26">
+        <v>300</v>
+      </c>
+      <c r="J26" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" t="s">
+        <v>17</v>
+      </c>
+      <c r="L26">
+        <v>120</v>
+      </c>
+      <c r="M26">
+        <v>16</v>
+      </c>
+      <c r="N26" t="s">
+        <v>17</v>
+      </c>
+      <c r="O26" t="s">
+        <v>17</v>
+      </c>
+      <c r="P26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
+        <v>3591</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D27">
+        <v>30</v>
+      </c>
+      <c r="E27">
+        <v>10</v>
+      </c>
+      <c r="F27">
+        <v>10</v>
+      </c>
+      <c r="G27">
+        <v>120</v>
+      </c>
+      <c r="H27">
+        <v>300</v>
+      </c>
+      <c r="I27">
+        <v>300</v>
+      </c>
+      <c r="J27" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" t="s">
+        <v>17</v>
+      </c>
+      <c r="L27">
+        <v>120</v>
+      </c>
+      <c r="M27">
+        <v>16</v>
+      </c>
+      <c r="N27" t="s">
+        <v>17</v>
+      </c>
+      <c r="O27" t="s">
+        <v>17</v>
+      </c>
+      <c r="P27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
+        <v>3311</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C28" t="s">
+        <v>16</v>
+      </c>
+      <c r="D28">
+        <v>30</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28">
+        <v>10</v>
+      </c>
+      <c r="G28">
+        <v>120</v>
+      </c>
+      <c r="H28">
+        <v>300</v>
+      </c>
+      <c r="I28">
+        <v>300</v>
+      </c>
+      <c r="J28" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28" t="s">
+        <v>17</v>
+      </c>
+      <c r="L28">
+        <v>120</v>
+      </c>
+      <c r="M28">
+        <v>16</v>
+      </c>
+      <c r="N28" t="s">
+        <v>17</v>
+      </c>
+      <c r="O28" t="s">
+        <v>17</v>
+      </c>
+      <c r="P28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
+        <v>3276</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C29" t="s">
+        <v>16</v>
+      </c>
+      <c r="D29">
+        <v>30</v>
+      </c>
+      <c r="E29">
+        <v>10</v>
+      </c>
+      <c r="F29">
+        <v>10</v>
+      </c>
+      <c r="G29">
+        <v>120</v>
+      </c>
+      <c r="H29">
+        <v>300</v>
+      </c>
+      <c r="I29">
+        <v>300</v>
+      </c>
+      <c r="J29" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29" t="s">
+        <v>17</v>
+      </c>
+      <c r="L29">
+        <v>120</v>
+      </c>
+      <c r="M29">
+        <v>16</v>
+      </c>
+      <c r="N29" t="s">
+        <v>17</v>
+      </c>
+      <c r="O29" t="s">
+        <v>17</v>
+      </c>
+      <c r="P29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
+        <v>4365</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C30" t="s">
+        <v>16</v>
+      </c>
+      <c r="D30">
+        <v>30</v>
+      </c>
+      <c r="E30">
+        <v>10</v>
+      </c>
+      <c r="F30">
+        <v>10</v>
+      </c>
+      <c r="G30">
+        <v>120</v>
+      </c>
+      <c r="H30">
+        <v>300</v>
+      </c>
+      <c r="I30">
+        <v>300</v>
+      </c>
+      <c r="J30" t="s">
+        <v>16</v>
+      </c>
+      <c r="K30" t="s">
+        <v>17</v>
+      </c>
+      <c r="L30">
+        <v>120</v>
+      </c>
+      <c r="M30">
+        <v>16</v>
+      </c>
+      <c r="N30" t="s">
+        <v>17</v>
+      </c>
+      <c r="O30" t="s">
+        <v>17</v>
+      </c>
+      <c r="P30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
+        <v>4364</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C31" t="s">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <v>30</v>
+      </c>
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31">
+        <v>10</v>
+      </c>
+      <c r="G31">
+        <v>120</v>
+      </c>
+      <c r="H31">
+        <v>300</v>
+      </c>
+      <c r="I31">
+        <v>300</v>
+      </c>
+      <c r="J31" t="s">
+        <v>16</v>
+      </c>
+      <c r="K31" t="s">
+        <v>17</v>
+      </c>
+      <c r="L31">
+        <v>120</v>
+      </c>
+      <c r="M31">
+        <v>16</v>
+      </c>
+      <c r="N31" t="s">
+        <v>17</v>
+      </c>
+      <c r="O31" t="s">
+        <v>17</v>
+      </c>
+      <c r="P31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
+        <v>3299</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32">
+        <v>30</v>
+      </c>
+      <c r="E32">
+        <v>10</v>
+      </c>
+      <c r="F32">
+        <v>10</v>
+      </c>
+      <c r="G32">
+        <v>120</v>
+      </c>
+      <c r="H32">
+        <v>300</v>
+      </c>
+      <c r="I32">
+        <v>300</v>
+      </c>
+      <c r="J32" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32">
+        <v>120</v>
+      </c>
+      <c r="M32">
+        <v>16</v>
+      </c>
+      <c r="N32" t="s">
+        <v>17</v>
+      </c>
+      <c r="O32" t="s">
+        <v>17</v>
+      </c>
+      <c r="P32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
+        <v>4638</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C33" t="s">
+        <v>16</v>
+      </c>
+      <c r="D33">
+        <v>30</v>
+      </c>
+      <c r="E33">
+        <v>10</v>
+      </c>
+      <c r="F33">
+        <v>10</v>
+      </c>
+      <c r="G33">
+        <v>120</v>
+      </c>
+      <c r="H33">
+        <v>300</v>
+      </c>
+      <c r="I33">
+        <v>300</v>
+      </c>
+      <c r="J33" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" t="s">
+        <v>17</v>
+      </c>
+      <c r="L33">
+        <v>120</v>
+      </c>
+      <c r="M33">
+        <v>16</v>
+      </c>
+      <c r="N33" t="s">
+        <v>17</v>
+      </c>
+      <c r="O33" t="s">
+        <v>17</v>
+      </c>
+      <c r="P33" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
+        <v>4362</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+      <c r="D34">
+        <v>30</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34">
+        <v>10</v>
+      </c>
+      <c r="G34">
+        <v>120</v>
+      </c>
+      <c r="H34">
+        <v>300</v>
+      </c>
+      <c r="I34">
+        <v>300</v>
+      </c>
+      <c r="J34" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" t="s">
+        <v>17</v>
+      </c>
+      <c r="L34">
+        <v>120</v>
+      </c>
+      <c r="M34">
+        <v>16</v>
+      </c>
+      <c r="N34" t="s">
+        <v>17</v>
+      </c>
+      <c r="O34" t="s">
+        <v>17</v>
+      </c>
+      <c r="P34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
+        <v>3267</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C35" t="s">
+        <v>16</v>
+      </c>
+      <c r="D35">
+        <v>30</v>
+      </c>
+      <c r="E35">
+        <v>10</v>
+      </c>
+      <c r="F35">
+        <v>10</v>
+      </c>
+      <c r="G35">
+        <v>120</v>
+      </c>
+      <c r="H35">
+        <v>300</v>
+      </c>
+      <c r="I35">
+        <v>300</v>
+      </c>
+      <c r="J35" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35" t="s">
+        <v>17</v>
+      </c>
+      <c r="L35">
+        <v>120</v>
+      </c>
+      <c r="M35">
+        <v>16</v>
+      </c>
+      <c r="N35" t="s">
+        <v>17</v>
+      </c>
+      <c r="O35" t="s">
+        <v>17</v>
+      </c>
+      <c r="P35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
+        <v>3285</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C36" t="s">
+        <v>16</v>
+      </c>
+      <c r="D36">
+        <v>30</v>
+      </c>
+      <c r="E36">
+        <v>10</v>
+      </c>
+      <c r="F36">
+        <v>10</v>
+      </c>
+      <c r="G36">
+        <v>120</v>
+      </c>
+      <c r="H36">
+        <v>300</v>
+      </c>
+      <c r="I36">
+        <v>300</v>
+      </c>
+      <c r="J36" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36" t="s">
+        <v>17</v>
+      </c>
+      <c r="L36">
+        <v>120</v>
+      </c>
+      <c r="M36">
+        <v>16</v>
+      </c>
+      <c r="N36" t="s">
+        <v>17</v>
+      </c>
+      <c r="O36" t="s">
+        <v>17</v>
+      </c>
+      <c r="P36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
+        <v>4641</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C37" t="s">
+        <v>16</v>
+      </c>
+      <c r="D37">
+        <v>30</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37">
+        <v>10</v>
+      </c>
+      <c r="G37">
+        <v>120</v>
+      </c>
+      <c r="H37">
+        <v>300</v>
+      </c>
+      <c r="I37">
+        <v>300</v>
+      </c>
+      <c r="J37" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37" t="s">
+        <v>17</v>
+      </c>
+      <c r="L37">
+        <v>120</v>
+      </c>
+      <c r="M37">
+        <v>16</v>
+      </c>
+      <c r="N37" t="s">
+        <v>17</v>
+      </c>
+      <c r="O37" t="s">
+        <v>17</v>
+      </c>
+      <c r="P37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
+        <v>3294</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C38" t="s">
+        <v>16</v>
+      </c>
+      <c r="D38">
+        <v>30</v>
+      </c>
+      <c r="E38">
+        <v>10</v>
+      </c>
+      <c r="F38">
+        <v>10</v>
+      </c>
+      <c r="G38">
+        <v>120</v>
+      </c>
+      <c r="H38">
+        <v>300</v>
+      </c>
+      <c r="I38">
+        <v>300</v>
+      </c>
+      <c r="J38" t="s">
+        <v>16</v>
+      </c>
+      <c r="K38" t="s">
+        <v>17</v>
+      </c>
+      <c r="L38">
+        <v>120</v>
+      </c>
+      <c r="M38">
+        <v>16</v>
+      </c>
+      <c r="N38" t="s">
+        <v>17</v>
+      </c>
+      <c r="O38" t="s">
+        <v>17</v>
+      </c>
+      <c r="P38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
+        <v>3305</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C39" t="s">
+        <v>16</v>
+      </c>
+      <c r="D39">
+        <v>30</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
+      </c>
+      <c r="G39">
+        <v>120</v>
+      </c>
+      <c r="H39">
+        <v>300</v>
+      </c>
+      <c r="I39">
+        <v>300</v>
+      </c>
+      <c r="J39" t="s">
+        <v>16</v>
+      </c>
+      <c r="K39" t="s">
+        <v>17</v>
+      </c>
+      <c r="L39">
+        <v>120</v>
+      </c>
+      <c r="M39">
+        <v>16</v>
+      </c>
+      <c r="N39" t="s">
+        <v>17</v>
+      </c>
+      <c r="O39" t="s">
+        <v>17</v>
+      </c>
+      <c r="P39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
+        <v>3595</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C40" t="s">
+        <v>16</v>
+      </c>
+      <c r="D40">
+        <v>30</v>
+      </c>
+      <c r="E40">
+        <v>10</v>
+      </c>
+      <c r="F40">
+        <v>10</v>
+      </c>
+      <c r="G40">
+        <v>120</v>
+      </c>
+      <c r="H40">
+        <v>300</v>
+      </c>
+      <c r="I40">
+        <v>300</v>
+      </c>
+      <c r="J40" t="s">
+        <v>16</v>
+      </c>
+      <c r="K40" t="s">
+        <v>17</v>
+      </c>
+      <c r="L40">
+        <v>120</v>
+      </c>
+      <c r="M40">
+        <v>16</v>
+      </c>
+      <c r="N40" t="s">
+        <v>17</v>
+      </c>
+      <c r="O40" t="s">
+        <v>17</v>
+      </c>
+      <c r="P40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
+        <v>3312</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D41">
+        <v>30</v>
+      </c>
+      <c r="E41">
+        <v>10</v>
+      </c>
+      <c r="F41">
+        <v>10</v>
+      </c>
+      <c r="G41">
+        <v>120</v>
+      </c>
+      <c r="H41">
+        <v>300</v>
+      </c>
+      <c r="I41">
+        <v>300</v>
+      </c>
+      <c r="J41" t="s">
+        <v>16</v>
+      </c>
+      <c r="K41" t="s">
+        <v>17</v>
+      </c>
+      <c r="L41">
+        <v>120</v>
+      </c>
+      <c r="M41">
+        <v>16</v>
+      </c>
+      <c r="N41" t="s">
+        <v>17</v>
+      </c>
+      <c r="O41" t="s">
+        <v>17</v>
+      </c>
+      <c r="P41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
+        <v>3286</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C42" t="s">
+        <v>16</v>
+      </c>
+      <c r="D42">
+        <v>30</v>
+      </c>
+      <c r="E42">
+        <v>10</v>
+      </c>
+      <c r="F42">
+        <v>10</v>
+      </c>
+      <c r="G42">
+        <v>120</v>
+      </c>
+      <c r="H42">
+        <v>300</v>
+      </c>
+      <c r="I42">
+        <v>300</v>
+      </c>
+      <c r="J42" t="s">
+        <v>16</v>
+      </c>
+      <c r="K42" t="s">
+        <v>17</v>
+      </c>
+      <c r="L42">
+        <v>120</v>
+      </c>
+      <c r="M42">
+        <v>16</v>
+      </c>
+      <c r="N42" t="s">
+        <v>17</v>
+      </c>
+      <c r="O42" t="s">
+        <v>17</v>
+      </c>
+      <c r="P42" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
+        <v>3275</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C43" t="s">
+        <v>16</v>
+      </c>
+      <c r="D43">
+        <v>30</v>
+      </c>
+      <c r="E43">
+        <v>10</v>
+      </c>
+      <c r="F43">
+        <v>10</v>
+      </c>
+      <c r="G43">
+        <v>120</v>
+      </c>
+      <c r="H43">
+        <v>300</v>
+      </c>
+      <c r="I43">
+        <v>300</v>
+      </c>
+      <c r="J43" t="s">
+        <v>16</v>
+      </c>
+      <c r="K43" t="s">
+        <v>17</v>
+      </c>
+      <c r="L43">
+        <v>120</v>
+      </c>
+      <c r="M43">
+        <v>16</v>
+      </c>
+      <c r="N43" t="s">
+        <v>17</v>
+      </c>
+      <c r="O43" t="s">
+        <v>17</v>
+      </c>
+      <c r="P43" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
+        <v>4347</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C44" t="s">
+        <v>16</v>
+      </c>
+      <c r="D44">
+        <v>30</v>
+      </c>
+      <c r="E44">
+        <v>10</v>
+      </c>
+      <c r="F44">
+        <v>10</v>
+      </c>
+      <c r="G44">
+        <v>120</v>
+      </c>
+      <c r="H44">
+        <v>300</v>
+      </c>
+      <c r="I44">
+        <v>300</v>
+      </c>
+      <c r="J44" t="s">
+        <v>16</v>
+      </c>
+      <c r="K44" t="s">
+        <v>17</v>
+      </c>
+      <c r="L44">
+        <v>120</v>
+      </c>
+      <c r="M44">
+        <v>16</v>
+      </c>
+      <c r="N44" t="s">
+        <v>17</v>
+      </c>
+      <c r="O44" t="s">
+        <v>17</v>
+      </c>
+      <c r="P44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
+        <v>3597</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C45" t="s">
+        <v>16</v>
+      </c>
+      <c r="D45">
+        <v>30</v>
+      </c>
+      <c r="E45">
+        <v>10</v>
+      </c>
+      <c r="F45">
+        <v>10</v>
+      </c>
+      <c r="G45">
+        <v>120</v>
+      </c>
+      <c r="H45">
+        <v>300</v>
+      </c>
+      <c r="I45">
+        <v>300</v>
+      </c>
+      <c r="J45" t="s">
+        <v>16</v>
+      </c>
+      <c r="K45" t="s">
+        <v>17</v>
+      </c>
+      <c r="L45">
+        <v>120</v>
+      </c>
+      <c r="M45">
+        <v>16</v>
+      </c>
+      <c r="N45" t="s">
+        <v>17</v>
+      </c>
+      <c r="O45" t="s">
+        <v>17</v>
+      </c>
+      <c r="P45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
+        <v>3310</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C46" t="s">
+        <v>16</v>
+      </c>
+      <c r="D46">
+        <v>30</v>
+      </c>
+      <c r="E46">
+        <v>10</v>
+      </c>
+      <c r="F46">
+        <v>10</v>
+      </c>
+      <c r="G46">
+        <v>120</v>
+      </c>
+      <c r="H46">
+        <v>300</v>
+      </c>
+      <c r="I46">
+        <v>300</v>
+      </c>
+      <c r="J46" t="s">
+        <v>16</v>
+      </c>
+      <c r="K46" t="s">
+        <v>17</v>
+      </c>
+      <c r="L46">
+        <v>120</v>
+      </c>
+      <c r="M46">
+        <v>16</v>
+      </c>
+      <c r="N46" t="s">
+        <v>17</v>
+      </c>
+      <c r="O46" t="s">
+        <v>17</v>
+      </c>
+      <c r="P46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
+        <v>4615</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C47" t="s">
+        <v>16</v>
+      </c>
+      <c r="D47">
+        <v>30</v>
+      </c>
+      <c r="E47">
+        <v>10</v>
+      </c>
+      <c r="F47">
+        <v>10</v>
+      </c>
+      <c r="G47">
+        <v>120</v>
+      </c>
+      <c r="H47">
+        <v>300</v>
+      </c>
+      <c r="I47">
+        <v>300</v>
+      </c>
+      <c r="J47" t="s">
+        <v>16</v>
+      </c>
+      <c r="K47" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47">
+        <v>120</v>
+      </c>
+      <c r="M47">
+        <v>16</v>
+      </c>
+      <c r="N47" t="s">
+        <v>17</v>
+      </c>
+      <c r="O47" t="s">
+        <v>17</v>
+      </c>
+      <c r="P47" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
+        <v>4619</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C48" t="s">
+        <v>16</v>
+      </c>
+      <c r="D48">
+        <v>30</v>
+      </c>
+      <c r="E48">
+        <v>10</v>
+      </c>
+      <c r="F48">
+        <v>10</v>
+      </c>
+      <c r="G48">
+        <v>120</v>
+      </c>
+      <c r="H48">
+        <v>300</v>
+      </c>
+      <c r="I48">
+        <v>300</v>
+      </c>
+      <c r="J48" t="s">
+        <v>16</v>
+      </c>
+      <c r="K48" t="s">
+        <v>17</v>
+      </c>
+      <c r="L48">
+        <v>120</v>
+      </c>
+      <c r="M48">
+        <v>16</v>
+      </c>
+      <c r="N48" t="s">
+        <v>17</v>
+      </c>
+      <c r="O48" t="s">
+        <v>17</v>
+      </c>
+      <c r="P48" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A49" s="2">
+        <v>4620</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C49" t="s">
+        <v>16</v>
+      </c>
+      <c r="D49">
+        <v>30</v>
+      </c>
+      <c r="E49">
+        <v>10</v>
+      </c>
+      <c r="F49">
+        <v>10</v>
+      </c>
+      <c r="G49">
+        <v>120</v>
+      </c>
+      <c r="H49">
+        <v>300</v>
+      </c>
+      <c r="I49">
+        <v>300</v>
+      </c>
+      <c r="J49" t="s">
+        <v>16</v>
+      </c>
+      <c r="K49" t="s">
+        <v>17</v>
+      </c>
+      <c r="L49">
+        <v>120</v>
+      </c>
+      <c r="M49">
+        <v>16</v>
+      </c>
+      <c r="N49" t="s">
+        <v>17</v>
+      </c>
+      <c r="O49" t="s">
+        <v>17</v>
+      </c>
+      <c r="P49" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A50" s="2">
+        <v>4560</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C50" t="s">
+        <v>16</v>
+      </c>
+      <c r="D50">
+        <v>30</v>
+      </c>
+      <c r="E50">
+        <v>10</v>
+      </c>
+      <c r="F50">
+        <v>10</v>
+      </c>
+      <c r="G50">
+        <v>120</v>
+      </c>
+      <c r="H50">
+        <v>300</v>
+      </c>
+      <c r="I50">
+        <v>300</v>
+      </c>
+      <c r="J50" t="s">
+        <v>16</v>
+      </c>
+      <c r="K50" t="s">
+        <v>17</v>
+      </c>
+      <c r="L50">
+        <v>120</v>
+      </c>
+      <c r="M50">
+        <v>16</v>
+      </c>
+      <c r="N50" t="s">
+        <v>17</v>
+      </c>
+      <c r="O50" t="s">
+        <v>17</v>
+      </c>
+      <c r="P50" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A51" s="2">
+        <v>4163</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C51" t="s">
+        <v>16</v>
+      </c>
+      <c r="D51">
+        <v>30</v>
+      </c>
+      <c r="E51">
+        <v>10</v>
+      </c>
+      <c r="F51">
+        <v>10</v>
+      </c>
+      <c r="G51">
+        <v>120</v>
+      </c>
+      <c r="H51">
+        <v>300</v>
+      </c>
+      <c r="I51">
+        <v>300</v>
+      </c>
+      <c r="J51" t="s">
+        <v>16</v>
+      </c>
+      <c r="K51" t="s">
+        <v>17</v>
+      </c>
+      <c r="L51">
+        <v>120</v>
+      </c>
+      <c r="M51">
+        <v>16</v>
+      </c>
+      <c r="N51" t="s">
+        <v>17</v>
+      </c>
+      <c r="O51" t="s">
+        <v>17</v>
+      </c>
+      <c r="P51" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
+        <v>4161</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C52" t="s">
+        <v>16</v>
+      </c>
+      <c r="D52">
+        <v>30</v>
+      </c>
+      <c r="E52">
+        <v>10</v>
+      </c>
+      <c r="F52">
+        <v>10</v>
+      </c>
+      <c r="G52">
+        <v>120</v>
+      </c>
+      <c r="H52">
+        <v>300</v>
+      </c>
+      <c r="I52">
+        <v>300</v>
+      </c>
+      <c r="J52" t="s">
+        <v>16</v>
+      </c>
+      <c r="K52" t="s">
+        <v>17</v>
+      </c>
+      <c r="L52">
+        <v>120</v>
+      </c>
+      <c r="M52">
+        <v>16</v>
+      </c>
+      <c r="N52" t="s">
+        <v>17</v>
+      </c>
+      <c r="O52" t="s">
+        <v>17</v>
+      </c>
+      <c r="P52" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
+        <v>4782</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C53" t="s">
+        <v>16</v>
+      </c>
+      <c r="D53">
+        <v>30</v>
+      </c>
+      <c r="E53">
+        <v>10</v>
+      </c>
+      <c r="F53">
+        <v>10</v>
+      </c>
+      <c r="G53">
+        <v>120</v>
+      </c>
+      <c r="H53">
+        <v>300</v>
+      </c>
+      <c r="I53">
+        <v>300</v>
+      </c>
+      <c r="J53" t="s">
+        <v>16</v>
+      </c>
+      <c r="K53" t="s">
+        <v>17</v>
+      </c>
+      <c r="L53">
+        <v>120</v>
+      </c>
+      <c r="M53">
+        <v>16</v>
+      </c>
+      <c r="N53" t="s">
+        <v>17</v>
+      </c>
+      <c r="O53" t="s">
+        <v>17</v>
+      </c>
+      <c r="P53" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
+        <v>4626</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C54" t="s">
+        <v>16</v>
+      </c>
+      <c r="D54">
+        <v>30</v>
+      </c>
+      <c r="E54">
+        <v>10</v>
+      </c>
+      <c r="F54">
+        <v>10</v>
+      </c>
+      <c r="G54">
+        <v>120</v>
+      </c>
+      <c r="H54">
+        <v>300</v>
+      </c>
+      <c r="I54">
+        <v>300</v>
+      </c>
+      <c r="J54" t="s">
+        <v>16</v>
+      </c>
+      <c r="K54" t="s">
+        <v>17</v>
+      </c>
+      <c r="L54">
+        <v>120</v>
+      </c>
+      <c r="M54">
+        <v>16</v>
+      </c>
+      <c r="N54" t="s">
+        <v>17</v>
+      </c>
+      <c r="O54" t="s">
+        <v>17</v>
+      </c>
+      <c r="P54" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
+        <v>4625</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C55" t="s">
+        <v>16</v>
+      </c>
+      <c r="D55">
+        <v>30</v>
+      </c>
+      <c r="E55">
+        <v>10</v>
+      </c>
+      <c r="F55">
+        <v>10</v>
+      </c>
+      <c r="G55">
+        <v>120</v>
+      </c>
+      <c r="H55">
+        <v>300</v>
+      </c>
+      <c r="I55">
+        <v>300</v>
+      </c>
+      <c r="J55" t="s">
+        <v>16</v>
+      </c>
+      <c r="K55" t="s">
+        <v>17</v>
+      </c>
+      <c r="L55">
+        <v>120</v>
+      </c>
+      <c r="M55">
+        <v>16</v>
+      </c>
+      <c r="N55" t="s">
+        <v>17</v>
+      </c>
+      <c r="O55" t="s">
+        <v>17</v>
+      </c>
+      <c r="P55" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
+        <v>4628</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C56" t="s">
+        <v>16</v>
+      </c>
+      <c r="D56">
+        <v>30</v>
+      </c>
+      <c r="E56">
+        <v>10</v>
+      </c>
+      <c r="F56">
+        <v>10</v>
+      </c>
+      <c r="G56">
+        <v>120</v>
+      </c>
+      <c r="H56">
+        <v>300</v>
+      </c>
+      <c r="I56">
+        <v>300</v>
+      </c>
+      <c r="J56" t="s">
+        <v>16</v>
+      </c>
+      <c r="K56" t="s">
+        <v>17</v>
+      </c>
+      <c r="L56">
+        <v>120</v>
+      </c>
+      <c r="M56">
+        <v>16</v>
+      </c>
+      <c r="N56" t="s">
+        <v>17</v>
+      </c>
+      <c r="O56" t="s">
+        <v>17</v>
+      </c>
+      <c r="P56" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
+        <v>4627</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C57" t="s">
+        <v>16</v>
+      </c>
+      <c r="D57">
+        <v>30</v>
+      </c>
+      <c r="E57">
+        <v>10</v>
+      </c>
+      <c r="F57">
+        <v>10</v>
+      </c>
+      <c r="G57">
+        <v>120</v>
+      </c>
+      <c r="H57">
+        <v>300</v>
+      </c>
+      <c r="I57">
+        <v>300</v>
+      </c>
+      <c r="J57" t="s">
+        <v>16</v>
+      </c>
+      <c r="K57" t="s">
+        <v>17</v>
+      </c>
+      <c r="L57">
+        <v>120</v>
+      </c>
+      <c r="M57">
+        <v>16</v>
+      </c>
+      <c r="N57" t="s">
+        <v>17</v>
+      </c>
+      <c r="O57" t="s">
+        <v>17</v>
+      </c>
+      <c r="P57" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
+        <v>4633</v>
+      </c>
+      <c r="B58" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C58" t="s">
+        <v>16</v>
+      </c>
+      <c r="D58">
+        <v>30</v>
+      </c>
+      <c r="E58">
+        <v>10</v>
+      </c>
+      <c r="F58">
+        <v>10</v>
+      </c>
+      <c r="G58">
+        <v>120</v>
+      </c>
+      <c r="H58">
+        <v>300</v>
+      </c>
+      <c r="I58">
+        <v>300</v>
+      </c>
+      <c r="J58" t="s">
+        <v>16</v>
+      </c>
+      <c r="K58" t="s">
+        <v>17</v>
+      </c>
+      <c r="L58">
+        <v>120</v>
+      </c>
+      <c r="M58">
+        <v>16</v>
+      </c>
+      <c r="N58" t="s">
+        <v>17</v>
+      </c>
+      <c r="O58" t="s">
+        <v>17</v>
+      </c>
+      <c r="P58" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A59" s="2">
+        <v>3302</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C59" t="s">
+        <v>16</v>
+      </c>
+      <c r="D59">
+        <v>30</v>
+      </c>
+      <c r="E59">
+        <v>10</v>
+      </c>
+      <c r="F59">
+        <v>10</v>
+      </c>
+      <c r="G59">
+        <v>120</v>
+      </c>
+      <c r="H59">
+        <v>300</v>
+      </c>
+      <c r="I59">
+        <v>300</v>
+      </c>
+      <c r="J59" t="s">
+        <v>16</v>
+      </c>
+      <c r="K59" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59">
+        <v>120</v>
+      </c>
+      <c r="M59">
+        <v>16</v>
+      </c>
+      <c r="N59" t="s">
+        <v>17</v>
+      </c>
+      <c r="O59" t="s">
+        <v>17</v>
+      </c>
+      <c r="P59" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
+        <v>4630</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C60" t="s">
+        <v>16</v>
+      </c>
+      <c r="D60">
+        <v>30</v>
+      </c>
+      <c r="E60">
+        <v>10</v>
+      </c>
+      <c r="F60">
+        <v>10</v>
+      </c>
+      <c r="G60">
+        <v>120</v>
+      </c>
+      <c r="H60">
+        <v>300</v>
+      </c>
+      <c r="I60">
+        <v>300</v>
+      </c>
+      <c r="J60" t="s">
+        <v>16</v>
+      </c>
+      <c r="K60" t="s">
+        <v>17</v>
+      </c>
+      <c r="L60">
+        <v>120</v>
+      </c>
+      <c r="M60">
+        <v>16</v>
+      </c>
+      <c r="N60" t="s">
+        <v>17</v>
+      </c>
+      <c r="O60" t="s">
+        <v>17</v>
+      </c>
+      <c r="P60" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
+        <v>4623</v>
+      </c>
+      <c r="B61" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C61" t="s">
+        <v>16</v>
+      </c>
+      <c r="D61">
+        <v>30</v>
+      </c>
+      <c r="E61">
+        <v>10</v>
+      </c>
+      <c r="F61">
+        <v>10</v>
+      </c>
+      <c r="G61">
+        <v>120</v>
+      </c>
+      <c r="H61">
+        <v>300</v>
+      </c>
+      <c r="I61">
+        <v>300</v>
+      </c>
+      <c r="J61" t="s">
+        <v>16</v>
+      </c>
+      <c r="K61" t="s">
+        <v>17</v>
+      </c>
+      <c r="L61">
+        <v>120</v>
+      </c>
+      <c r="M61">
+        <v>16</v>
+      </c>
+      <c r="N61" t="s">
+        <v>17</v>
+      </c>
+      <c r="O61" t="s">
+        <v>17</v>
+      </c>
+      <c r="P61" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
+        <v>4624</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C62" t="s">
+        <v>16</v>
+      </c>
+      <c r="D62">
+        <v>30</v>
+      </c>
+      <c r="E62">
+        <v>10</v>
+      </c>
+      <c r="F62">
+        <v>10</v>
+      </c>
+      <c r="G62">
+        <v>120</v>
+      </c>
+      <c r="H62">
+        <v>300</v>
+      </c>
+      <c r="I62">
+        <v>300</v>
+      </c>
+      <c r="J62" t="s">
+        <v>16</v>
+      </c>
+      <c r="K62" t="s">
+        <v>17</v>
+      </c>
+      <c r="L62">
+        <v>120</v>
+      </c>
+      <c r="M62">
+        <v>16</v>
+      </c>
+      <c r="N62" t="s">
+        <v>17</v>
+      </c>
+      <c r="O62" t="s">
+        <v>17</v>
+      </c>
+      <c r="P62" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
+        <v>4622</v>
+      </c>
+      <c r="B63" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C63" t="s">
+        <v>16</v>
+      </c>
+      <c r="D63">
+        <v>30</v>
+      </c>
+      <c r="E63">
+        <v>10</v>
+      </c>
+      <c r="F63">
+        <v>10</v>
+      </c>
+      <c r="G63">
+        <v>120</v>
+      </c>
+      <c r="H63">
+        <v>300</v>
+      </c>
+      <c r="I63">
+        <v>300</v>
+      </c>
+      <c r="J63" t="s">
+        <v>16</v>
+      </c>
+      <c r="K63" t="s">
+        <v>17</v>
+      </c>
+      <c r="L63">
+        <v>120</v>
+      </c>
+      <c r="M63">
+        <v>16</v>
+      </c>
+      <c r="N63" t="s">
+        <v>17</v>
+      </c>
+      <c r="O63" t="s">
+        <v>17</v>
+      </c>
+      <c r="P63" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A64" s="2">
+        <v>4516</v>
+      </c>
+      <c r="B64" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C64" t="s">
+        <v>16</v>
+      </c>
+      <c r="D64">
+        <v>30</v>
+      </c>
+      <c r="E64">
+        <v>10</v>
+      </c>
+      <c r="F64">
+        <v>10</v>
+      </c>
+      <c r="G64">
+        <v>120</v>
+      </c>
+      <c r="H64">
+        <v>300</v>
+      </c>
+      <c r="I64">
+        <v>300</v>
+      </c>
+      <c r="J64" t="s">
+        <v>16</v>
+      </c>
+      <c r="K64" t="s">
+        <v>17</v>
+      </c>
+      <c r="L64">
+        <v>120</v>
+      </c>
+      <c r="M64">
+        <v>16</v>
+      </c>
+      <c r="N64" t="s">
+        <v>17</v>
+      </c>
+      <c r="O64" t="s">
+        <v>17</v>
+      </c>
+      <c r="P64" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A65" s="2">
+        <v>9078</v>
+      </c>
+      <c r="B65" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C65" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65">
+        <v>30</v>
+      </c>
+      <c r="E65">
+        <v>10</v>
+      </c>
+      <c r="F65">
+        <v>10</v>
+      </c>
+      <c r="G65">
+        <v>120</v>
+      </c>
+      <c r="H65">
+        <v>300</v>
+      </c>
+      <c r="I65">
+        <v>300</v>
+      </c>
+      <c r="J65" t="s">
+        <v>16</v>
+      </c>
+      <c r="K65" t="s">
+        <v>17</v>
+      </c>
+      <c r="L65">
+        <v>120</v>
+      </c>
+      <c r="M65">
+        <v>16</v>
+      </c>
+      <c r="N65" t="s">
+        <v>17</v>
+      </c>
+      <c r="O65" t="s">
+        <v>17</v>
+      </c>
+      <c r="P65" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A66" s="2">
+        <v>4635</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C66" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66">
+        <v>30</v>
+      </c>
+      <c r="E66">
+        <v>10</v>
+      </c>
+      <c r="F66">
+        <v>10</v>
+      </c>
+      <c r="G66">
+        <v>120</v>
+      </c>
+      <c r="H66">
+        <v>300</v>
+      </c>
+      <c r="I66">
+        <v>300</v>
+      </c>
+      <c r="J66" t="s">
+        <v>16</v>
+      </c>
+      <c r="K66" t="s">
+        <v>17</v>
+      </c>
+      <c r="L66">
+        <v>120</v>
+      </c>
+      <c r="M66">
+        <v>16</v>
+      </c>
+      <c r="N66" t="s">
+        <v>17</v>
+      </c>
+      <c r="O66" t="s">
+        <v>17</v>
+      </c>
+      <c r="P66" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A67" s="2">
+        <v>4632</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C67" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67">
+        <v>30</v>
+      </c>
+      <c r="E67">
+        <v>10</v>
+      </c>
+      <c r="F67">
+        <v>10</v>
+      </c>
+      <c r="G67">
+        <v>120</v>
+      </c>
+      <c r="H67">
+        <v>300</v>
+      </c>
+      <c r="I67">
+        <v>300</v>
+      </c>
+      <c r="J67" t="s">
+        <v>16</v>
+      </c>
+      <c r="K67" t="s">
+        <v>17</v>
+      </c>
+      <c r="L67">
+        <v>120</v>
+      </c>
+      <c r="M67">
+        <v>16</v>
+      </c>
+      <c r="N67" t="s">
+        <v>17</v>
+      </c>
+      <c r="O67" t="s">
+        <v>17</v>
+      </c>
+      <c r="P67" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A68" s="2">
+        <v>4634</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C68" t="s">
+        <v>16</v>
+      </c>
+      <c r="D68">
+        <v>30</v>
+      </c>
+      <c r="E68">
+        <v>10</v>
+      </c>
+      <c r="F68">
+        <v>10</v>
+      </c>
+      <c r="G68">
+        <v>120</v>
+      </c>
+      <c r="H68">
+        <v>300</v>
+      </c>
+      <c r="I68">
+        <v>300</v>
+      </c>
+      <c r="J68" t="s">
+        <v>16</v>
+      </c>
+      <c r="K68" t="s">
+        <v>17</v>
+      </c>
+      <c r="L68">
+        <v>120</v>
+      </c>
+      <c r="M68">
+        <v>16</v>
+      </c>
+      <c r="N68" t="s">
+        <v>17</v>
+      </c>
+      <c r="O68" t="s">
+        <v>17</v>
+      </c>
+      <c r="P68" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A69" s="2">
+        <v>4629</v>
+      </c>
+      <c r="B69" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C69" t="s">
+        <v>16</v>
+      </c>
+      <c r="D69">
+        <v>30</v>
+      </c>
+      <c r="E69">
+        <v>10</v>
+      </c>
+      <c r="F69">
+        <v>10</v>
+      </c>
+      <c r="G69">
+        <v>120</v>
+      </c>
+      <c r="H69">
+        <v>300</v>
+      </c>
+      <c r="I69">
+        <v>300</v>
+      </c>
+      <c r="J69" t="s">
+        <v>16</v>
+      </c>
+      <c r="K69" t="s">
+        <v>17</v>
+      </c>
+      <c r="L69">
+        <v>120</v>
+      </c>
+      <c r="M69">
+        <v>16</v>
+      </c>
+      <c r="N69" t="s">
+        <v>17</v>
+      </c>
+      <c r="O69" t="s">
+        <v>17</v>
+      </c>
+      <c r="P69" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A70" s="2">
+        <v>4631</v>
+      </c>
+      <c r="B70" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C70" t="s">
+        <v>16</v>
+      </c>
+      <c r="D70">
+        <v>30</v>
+      </c>
+      <c r="E70">
+        <v>10</v>
+      </c>
+      <c r="F70">
+        <v>10</v>
+      </c>
+      <c r="G70">
+        <v>120</v>
+      </c>
+      <c r="H70">
+        <v>300</v>
+      </c>
+      <c r="I70">
+        <v>300</v>
+      </c>
+      <c r="J70" t="s">
+        <v>16</v>
+      </c>
+      <c r="K70" t="s">
+        <v>17</v>
+      </c>
+      <c r="L70">
+        <v>120</v>
+      </c>
+      <c r="M70">
+        <v>16</v>
+      </c>
+      <c r="N70" t="s">
+        <v>17</v>
+      </c>
+      <c r="O70" t="s">
+        <v>17</v>
+      </c>
+      <c r="P70" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A71" s="2">
+        <v>4621</v>
+      </c>
+      <c r="B71" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C71" t="s">
+        <v>16</v>
+      </c>
+      <c r="D71">
+        <v>30</v>
+      </c>
+      <c r="E71">
+        <v>10</v>
+      </c>
+      <c r="F71">
+        <v>10</v>
+      </c>
+      <c r="G71">
+        <v>120</v>
+      </c>
+      <c r="H71">
+        <v>300</v>
+      </c>
+      <c r="I71">
+        <v>300</v>
+      </c>
+      <c r="J71" t="s">
+        <v>16</v>
+      </c>
+      <c r="K71" t="s">
+        <v>17</v>
+      </c>
+      <c r="L71">
+        <v>120</v>
+      </c>
+      <c r="M71">
+        <v>16</v>
+      </c>
+      <c r="N71" t="s">
+        <v>17</v>
+      </c>
+      <c r="O71" t="s">
+        <v>17</v>
+      </c>
+      <c r="P71" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A72" s="2">
+        <v>4162</v>
+      </c>
+      <c r="B72" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C72" t="s">
+        <v>16</v>
+      </c>
+      <c r="D72">
+        <v>30</v>
+      </c>
+      <c r="E72">
+        <v>10</v>
+      </c>
+      <c r="F72">
+        <v>10</v>
+      </c>
+      <c r="G72">
+        <v>120</v>
+      </c>
+      <c r="H72">
+        <v>300</v>
+      </c>
+      <c r="I72">
+        <v>300</v>
+      </c>
+      <c r="J72" t="s">
+        <v>16</v>
+      </c>
+      <c r="K72" t="s">
+        <v>17</v>
+      </c>
+      <c r="L72">
+        <v>120</v>
+      </c>
+      <c r="M72">
+        <v>16</v>
+      </c>
+      <c r="N72" t="s">
+        <v>17</v>
+      </c>
+      <c r="O72" t="s">
+        <v>17</v>
+      </c>
+      <c r="P72" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A73" s="2">
+        <v>3313</v>
+      </c>
+      <c r="B73" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C73" t="s">
+        <v>16</v>
+      </c>
+      <c r="D73">
+        <v>30</v>
+      </c>
+      <c r="E73">
+        <v>10</v>
+      </c>
+      <c r="F73">
+        <v>10</v>
+      </c>
+      <c r="G73">
+        <v>120</v>
+      </c>
+      <c r="H73">
+        <v>300</v>
+      </c>
+      <c r="I73">
+        <v>300</v>
+      </c>
+      <c r="J73" t="s">
+        <v>16</v>
+      </c>
+      <c r="K73" t="s">
+        <v>17</v>
+      </c>
+      <c r="L73">
+        <v>120</v>
+      </c>
+      <c r="M73">
+        <v>16</v>
+      </c>
+      <c r="N73" t="s">
+        <v>17</v>
+      </c>
+      <c r="O73" t="s">
+        <v>17</v>
+      </c>
+      <c r="P73" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A74" s="2">
+        <v>4785</v>
+      </c>
+      <c r="B74" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C74" t="s">
+        <v>16</v>
+      </c>
+      <c r="D74">
+        <v>30</v>
+      </c>
+      <c r="E74">
+        <v>10</v>
+      </c>
+      <c r="F74">
+        <v>10</v>
+      </c>
+      <c r="G74">
+        <v>120</v>
+      </c>
+      <c r="H74">
+        <v>300</v>
+      </c>
+      <c r="I74">
+        <v>300</v>
+      </c>
+      <c r="J74" t="s">
+        <v>16</v>
+      </c>
+      <c r="K74" t="s">
+        <v>17</v>
+      </c>
+      <c r="L74">
+        <v>120</v>
+      </c>
+      <c r="M74">
+        <v>16</v>
+      </c>
+      <c r="N74" t="s">
+        <v>17</v>
+      </c>
+      <c r="O74" t="s">
+        <v>17</v>
+      </c>
+      <c r="P74" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A75" s="2">
+        <v>4642</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C75" t="s">
+        <v>16</v>
+      </c>
+      <c r="D75">
+        <v>30</v>
+      </c>
+      <c r="E75">
+        <v>10</v>
+      </c>
+      <c r="F75">
+        <v>10</v>
+      </c>
+      <c r="G75">
+        <v>120</v>
+      </c>
+      <c r="H75">
+        <v>300</v>
+      </c>
+      <c r="I75">
+        <v>300</v>
+      </c>
+      <c r="J75" t="s">
+        <v>16</v>
+      </c>
+      <c r="K75" t="s">
+        <v>17</v>
+      </c>
+      <c r="L75">
+        <v>120</v>
+      </c>
+      <c r="M75">
+        <v>16</v>
+      </c>
+      <c r="N75" t="s">
+        <v>17</v>
+      </c>
+      <c r="O75" t="s">
+        <v>17</v>
+      </c>
+      <c r="P75" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A76" s="2">
+        <v>4781</v>
+      </c>
+      <c r="B76" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C76" t="s">
+        <v>16</v>
+      </c>
+      <c r="D76">
+        <v>30</v>
+      </c>
+      <c r="E76">
+        <v>10</v>
+      </c>
+      <c r="F76">
+        <v>10</v>
+      </c>
+      <c r="G76">
+        <v>120</v>
+      </c>
+      <c r="H76">
+        <v>300</v>
+      </c>
+      <c r="I76">
+        <v>300</v>
+      </c>
+      <c r="J76" t="s">
+        <v>16</v>
+      </c>
+      <c r="K76" t="s">
+        <v>17</v>
+      </c>
+      <c r="L76">
+        <v>120</v>
+      </c>
+      <c r="M76">
+        <v>16</v>
+      </c>
+      <c r="N76" t="s">
+        <v>17</v>
+      </c>
+      <c r="O76" t="s">
+        <v>17</v>
+      </c>
+      <c r="P76" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A77" s="2">
+        <v>6178</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C77" t="s">
+        <v>16</v>
+      </c>
+      <c r="D77">
+        <v>30</v>
+      </c>
+      <c r="E77">
+        <v>10</v>
+      </c>
+      <c r="F77">
+        <v>10</v>
+      </c>
+      <c r="G77">
+        <v>120</v>
+      </c>
+      <c r="H77">
+        <v>300</v>
+      </c>
+      <c r="I77">
+        <v>300</v>
+      </c>
+      <c r="J77" t="s">
+        <v>16</v>
+      </c>
+      <c r="K77" t="s">
+        <v>17</v>
+      </c>
+      <c r="L77">
+        <v>120</v>
+      </c>
+      <c r="M77">
+        <v>16</v>
+      </c>
+      <c r="N77" t="s">
+        <v>17</v>
+      </c>
+      <c r="O77" t="s">
+        <v>17</v>
+      </c>
+      <c r="P77" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A78" s="2">
+        <v>6158</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C78" t="s">
+        <v>16</v>
+      </c>
+      <c r="D78">
+        <v>30</v>
+      </c>
+      <c r="E78">
+        <v>10</v>
+      </c>
+      <c r="F78">
+        <v>10</v>
+      </c>
+      <c r="G78">
+        <v>120</v>
+      </c>
+      <c r="H78">
+        <v>300</v>
+      </c>
+      <c r="I78">
+        <v>300</v>
+      </c>
+      <c r="J78" t="s">
+        <v>16</v>
+      </c>
+      <c r="K78" t="s">
+        <v>17</v>
+      </c>
+      <c r="L78">
+        <v>120</v>
+      </c>
+      <c r="M78">
+        <v>16</v>
+      </c>
+      <c r="N78" t="s">
+        <v>17</v>
+      </c>
+      <c r="O78" t="s">
+        <v>17</v>
+      </c>
+      <c r="P78" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A79" s="2">
+        <v>6179</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C79" t="s">
+        <v>16</v>
+      </c>
+      <c r="D79">
+        <v>30</v>
+      </c>
+      <c r="E79">
+        <v>10</v>
+      </c>
+      <c r="F79">
+        <v>10</v>
+      </c>
+      <c r="G79">
+        <v>120</v>
+      </c>
+      <c r="H79">
+        <v>300</v>
+      </c>
+      <c r="I79">
+        <v>300</v>
+      </c>
+      <c r="J79" t="s">
+        <v>16</v>
+      </c>
+      <c r="K79" t="s">
+        <v>17</v>
+      </c>
+      <c r="L79">
+        <v>120</v>
+      </c>
+      <c r="M79">
+        <v>16</v>
+      </c>
+      <c r="N79" t="s">
+        <v>17</v>
+      </c>
+      <c r="O79" t="s">
+        <v>17</v>
+      </c>
+      <c r="P79" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A80" s="2">
+        <v>6157</v>
+      </c>
+      <c r="B80" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C80" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80">
+        <v>30</v>
+      </c>
+      <c r="E80">
+        <v>10</v>
+      </c>
+      <c r="F80">
+        <v>10</v>
+      </c>
+      <c r="G80">
+        <v>120</v>
+      </c>
+      <c r="H80">
+        <v>300</v>
+      </c>
+      <c r="I80">
+        <v>300</v>
+      </c>
+      <c r="J80" t="s">
+        <v>16</v>
+      </c>
+      <c r="K80" t="s">
+        <v>17</v>
+      </c>
+      <c r="L80">
+        <v>120</v>
+      </c>
+      <c r="M80">
+        <v>16</v>
+      </c>
+      <c r="N80" t="s">
+        <v>17</v>
+      </c>
+      <c r="O80" t="s">
+        <v>17</v>
+      </c>
+      <c r="P80" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A81" s="2">
+        <v>6180</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C81" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81">
+        <v>30</v>
+      </c>
+      <c r="E81">
+        <v>10</v>
+      </c>
+      <c r="F81">
+        <v>10</v>
+      </c>
+      <c r="G81">
+        <v>120</v>
+      </c>
+      <c r="H81">
+        <v>300</v>
+      </c>
+      <c r="I81">
+        <v>300</v>
+      </c>
+      <c r="J81" t="s">
+        <v>16</v>
+      </c>
+      <c r="K81" t="s">
+        <v>17</v>
+      </c>
+      <c r="L81">
+        <v>120</v>
+      </c>
+      <c r="M81">
+        <v>16</v>
+      </c>
+      <c r="N81" t="s">
+        <v>17</v>
+      </c>
+      <c r="O81" t="s">
+        <v>17</v>
+      </c>
+      <c r="P81" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A82" s="2">
+        <v>6159</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C82" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82">
+        <v>30</v>
+      </c>
+      <c r="E82">
+        <v>10</v>
+      </c>
+      <c r="F82">
+        <v>10</v>
+      </c>
+      <c r="G82">
+        <v>120</v>
+      </c>
+      <c r="H82">
+        <v>300</v>
+      </c>
+      <c r="I82">
+        <v>300</v>
+      </c>
+      <c r="J82" t="s">
+        <v>16</v>
+      </c>
+      <c r="K82" t="s">
+        <v>17</v>
+      </c>
+      <c r="L82">
+        <v>120</v>
+      </c>
+      <c r="M82">
+        <v>16</v>
+      </c>
+      <c r="N82" t="s">
+        <v>17</v>
+      </c>
+      <c r="O82" t="s">
+        <v>17</v>
+      </c>
+      <c r="P82" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A83" s="2">
+        <v>6177</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C83" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83">
+        <v>30</v>
+      </c>
+      <c r="E83">
+        <v>10</v>
+      </c>
+      <c r="F83">
+        <v>10</v>
+      </c>
+      <c r="G83">
+        <v>120</v>
+      </c>
+      <c r="H83">
+        <v>300</v>
+      </c>
+      <c r="I83">
+        <v>300</v>
+      </c>
+      <c r="J83" t="s">
+        <v>16</v>
+      </c>
+      <c r="K83" t="s">
+        <v>17</v>
+      </c>
+      <c r="L83">
+        <v>120</v>
+      </c>
+      <c r="M83">
+        <v>16</v>
+      </c>
+      <c r="N83" t="s">
+        <v>17</v>
+      </c>
+      <c r="O83" t="s">
+        <v>17</v>
+      </c>
+      <c r="P83" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A84" s="2">
+        <v>4786</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C84" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84">
+        <v>30</v>
+      </c>
+      <c r="E84">
+        <v>10</v>
+      </c>
+      <c r="F84">
+        <v>10</v>
+      </c>
+      <c r="G84">
+        <v>120</v>
+      </c>
+      <c r="H84">
+        <v>300</v>
+      </c>
+      <c r="I84">
+        <v>300</v>
+      </c>
+      <c r="J84" t="s">
+        <v>16</v>
+      </c>
+      <c r="K84" t="s">
+        <v>17</v>
+      </c>
+      <c r="L84">
+        <v>120</v>
+      </c>
+      <c r="M84">
+        <v>16</v>
+      </c>
+      <c r="N84" t="s">
+        <v>17</v>
+      </c>
+      <c r="O84" t="s">
+        <v>17</v>
+      </c>
+      <c r="P84" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A85" s="2">
+        <v>6156</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46082</v>
+      </c>
+      <c r="C85" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85">
+        <v>30</v>
+      </c>
+      <c r="E85">
+        <v>10</v>
+      </c>
+      <c r="F85">
+        <v>10</v>
+      </c>
+      <c r="G85">
+        <v>120</v>
+      </c>
+      <c r="H85">
+        <v>300</v>
+      </c>
+      <c r="I85">
+        <v>300</v>
+      </c>
+      <c r="J85" t="s">
+        <v>16</v>
+      </c>
+      <c r="K85" t="s">
+        <v>17</v>
+      </c>
+      <c r="L85">
+        <v>120</v>
+      </c>
+      <c r="M85">
+        <v>16</v>
+      </c>
+      <c r="N85" t="s">
+        <v>17</v>
+      </c>
+      <c r="O85" t="s">
+        <v>17</v>
+      </c>
+      <c r="P85" t="s">
         <v>17</v>
       </c>
     </row>
